--- a/ПЛАКАТЫ, ЧЕРТЕЖИ И ПРОЧЕЕ/ПЛАКАТ ЭРГОНОМИКА.xlsx
+++ b/ПЛАКАТЫ, ЧЕРТЕЖИ И ПРОЧЕЕ/ПЛАКАТ ЭРГОНОМИКА.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -399,7 +399,7 @@
                   <c:v>0.83</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.87</c:v>
+                  <c:v>0.86</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2358,12 +2358,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A4:J9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="8.7265625" style="2"/>
+    <col min="1" max="16384" width="8.7109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:10" ht="19" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="19" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -2385,18 +2385,18 @@
         <v>46178</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="3">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="C6" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="19.5" x14ac:dyDescent="0.25">
       <c r="H7" s="1" t="s">
         <v>0</v>
       </c>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" ht="19" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="19.5" x14ac:dyDescent="0.25">
       <c r="H8" s="3" t="s">
         <v>3</v>
       </c>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="J8" s="4"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="19.5" x14ac:dyDescent="0.25">
       <c r="H9" s="3" t="s">
         <v>4</v>
       </c>
